--- a/reports/20260506/API_stackranking.xlsx
+++ b/reports/20260506/API_stackranking.xlsx
@@ -160,13 +160,13 @@
     <t>Total Testcase Count:- 4</t>
   </si>
   <si>
-    <t>Started :- 06-05-2026 12:46</t>
-  </si>
-  <si>
-    <t>Ended :- 06-05-2026 12:46</t>
-  </si>
-  <si>
-    <t>passed cases06-05-2026 12:46</t>
+    <t>Started :- 06-05-2026 17:48</t>
+  </si>
+  <si>
+    <t>Ended :- 06-05-2026 17:48</t>
+  </si>
+  <si>
+    <t>passed cases06-05-2026 17:48</t>
   </si>
   <si>
     <t>failed cases</t>
